--- a/artfynd/A 1931-2025 artfynd.xlsx
+++ b/artfynd/A 1931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78710750</v>
+        <v>120651016</v>
       </c>
       <c r="B2" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223619</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karlsäng NO, 500 m, Ög</t>
+          <t>Landskarlstorget, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517739.2603278576</v>
+        <v>517796</v>
       </c>
       <c r="R2" t="n">
-        <v>6494893.058783899</v>
+        <v>6494966</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sporre &lt;25 mm</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,39 +761,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hedartad öppen plats (Landskarlstorget)</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Antonsson</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Antonsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Projekt Östergötland Flora</t>
-        </is>
-      </c>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120651016</v>
+        <v>119364761</v>
       </c>
       <c r="B3" t="n">
-        <v>91084</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,26 +787,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517796</v>
+        <v>517825</v>
       </c>
       <c r="R3" t="n">
-        <v>6494966</v>
+        <v>6494958</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,12 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +885,145 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Martin Berry</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Martin Berry</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>78710750</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Karlsäng NO, 500 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>517739</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6494893</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kristberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sporre &lt;25 mm</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hedartad öppen plats (Landskarlstorget)</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kjell Antonsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kjell Antonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Projekt Östergötland Flora</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
